--- a/data/trans_bre/IP16B03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Estudios-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,81</t>
+          <t>0,0; 53,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 116,48</t>
+          <t>0,0; 115,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,06</t>
+          <t>0,0; 34,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,46</t>
+          <t>0,0; 53,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Estudios-trans_bre.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,68</t>
+          <t>0,0; 52,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 115,89</t>
+          <t>0,0; 110,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,58</t>
+          <t>0,0; 37,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,26</t>
+          <t>0,0; 60,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
